--- a/artfynd/A 61388-2021 artfynd.xlsx
+++ b/artfynd/A 61388-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61388-2021 artfynd.xlsx
+++ b/artfynd/A 61388-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6784160</v>
+        <v>91486227</v>
       </c>
       <c r="B2" t="n">
-        <v>57193</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206004</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bäcken vid Ströbykärret, Upl</t>
+          <t>Falkstensmossen SO, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629547.6267816999</v>
+        <v>629415</v>
       </c>
       <c r="R2" t="n">
-        <v>6646042.015295709</v>
+        <v>6646112</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,32 +740,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Börje</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-06-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2021-03-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-06-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Det är alltför sällan man ser skogshare nu för tiden. Kul att det verkar finnas en population längs Börje Sjö-vägen.</t>
+          <t>2021-03-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,31 +761,36 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ragnar Hall</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ragnar Hall</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91486232</v>
+        <v>91486226</v>
       </c>
       <c r="B3" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -848,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629501.1474947156</v>
+        <v>629411</v>
       </c>
       <c r="R3" t="n">
-        <v>6646063.463505617</v>
+        <v>6646079</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,21 +860,11 @@
           <t>2021-03-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-03-06</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -912,7 +881,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>torrbjörk</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -930,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91486230</v>
+        <v>91486229</v>
       </c>
       <c r="B4" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>101735</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -975,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629483.3884068868</v>
+        <v>629416</v>
       </c>
       <c r="R4" t="n">
-        <v>6646068.359819274</v>
+        <v>6646125</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +964,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Börje</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1008,21 +972,11 @@
           <t>2021-03-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-03-06</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1039,7 +993,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1057,15 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91486226</v>
+        <v>91486230</v>
       </c>
       <c r="B5" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101735</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1102,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629411.144993764</v>
+        <v>629483</v>
       </c>
       <c r="R5" t="n">
-        <v>6646079.375500208</v>
+        <v>6646068</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,21 +1084,11 @@
           <t>2021-03-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-03-06</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1166,7 +1105,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,12 +1126,7 @@
         <v>91486231</v>
       </c>
       <c r="B6" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629483.3884068868</v>
+        <v>629483</v>
       </c>
       <c r="R6" t="n">
-        <v>6646068.359819274</v>
+        <v>6646068</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1262,19 +1196,9 @@
           <t>2021-03-06</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-03-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,6 +1232,1040 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>91486207</v>
+      </c>
+      <c r="B7" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Falkstensmossen SO, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>629455</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6646152</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Börje</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-03-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-03-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>död björk</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>91486205</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Falkstensmossen SO, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>629496</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6646189</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Börje</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-03-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-03-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>grova grenar på jättegran</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>91486204</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Falkstensmossen SO, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>629501</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6646199</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Börje</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-03-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-03-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>enstaka flyghål</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>grova granar</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>55909327</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bäcken vid Ströbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>629548</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6646042</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2015-11-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2015-11-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Först höstlätet med en lång vissling som första ton. Sedan även några sångstrofer. En större hackspett varnade intensivt när den fick syn på ugglan.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ragnar Hall</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ragnar Hall</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>55909321</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bäcken vid Ströbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>629548</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6646042</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2015-11-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2015-11-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ragnar Hall</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ragnar Hall</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>91486209</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Falkstensmossen SO, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>629455</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6646152</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Börje</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-03-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-03-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>död björk</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>91486232</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Falkstensmossen SO, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>629501</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6646063</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-03-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-03-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>torrbjörk</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6784160</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bäcken vid Ströbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>629548</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6646042</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2013-06-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2013-06-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Det är alltför sällan man ser skogshare nu för tiden. Kul att det verkar finnas en population längs Börje Sjö-vägen.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ragnar Hall</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ragnar Hall</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>91486206</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Falkstensmossen SO, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>629485</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6646195</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Börje</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-03-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-03-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
